--- a/80_Asset/設計資料/SNFramework.xlsx
+++ b/80_Asset/設計資料/SNFramework.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shinj\OneDrive\ドキュメント\Creation\ソフト開発\SNFramework\80_Asset\設計資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1C1C63-64B3-4453-B1D7-9638FDA4EC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F65323C-BF90-4AE9-B9FC-DE9EDEE4F60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-86" yWindow="0" windowWidth="16629" windowHeight="18600" activeTab="5" xr2:uid="{70336C66-D1CA-48C0-83F2-0D9D170A84BC}"/>
+    <workbookView xWindow="16371" yWindow="0" windowWidth="16629" windowHeight="18600" firstSheet="2" activeTab="6" xr2:uid="{70336C66-D1CA-48C0-83F2-0D9D170A84BC}"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="機能一覧" sheetId="33" r:id="rId4"/>
     <sheet name="スレッド構成" sheetId="34" r:id="rId5"/>
     <sheet name="アプリ構成" sheetId="35" r:id="rId6"/>
-    <sheet name="てんぷれ" sheetId="5" r:id="rId7"/>
+    <sheet name="アクティブオブジェクト状態遷移" sheetId="36" r:id="rId7"/>
+    <sheet name="てんぷれ" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="119">
   <si>
     <t>システム構成</t>
     <rPh sb="4" eb="6">
@@ -1009,6 +1010,86 @@
   </si>
   <si>
     <t>MenuAppのサブステート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクティブオブジェクト状態遷移</t>
+    <rPh sb="11" eb="13">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Idle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Walk</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Jog</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Wait</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Jump</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Knockback</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Spell</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Action</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Flying</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fall</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓イベント</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→状態</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stop</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Z速度&lt;0</t>
+    <rPh sb="1" eb="3">
+      <t>ソクド</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6346,6 +6427,431 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{166A535F-7008-47AE-B069-9AB336B6128F}">
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr defaultColWidth="3.5" defaultRowHeight="18.45"/>
+  <cols>
+    <col min="1" max="2" width="3.5" style="2"/>
+    <col min="3" max="3" width="10.640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.35546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.92578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.0703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.35546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="3.5" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="B2" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3">
+        <v>4</v>
+      </c>
+      <c r="H4" s="3">
+        <v>5</v>
+      </c>
+      <c r="I4" s="3">
+        <v>6</v>
+      </c>
+      <c r="J4" s="3">
+        <v>7</v>
+      </c>
+      <c r="K4" s="3">
+        <v>8</v>
+      </c>
+      <c r="L4" s="3">
+        <v>9</v>
+      </c>
+      <c r="M4" s="3">
+        <v>10</v>
+      </c>
+      <c r="N4" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3">
+        <v>2</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K6" s="3">
+        <v>2</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="B7" s="3">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3">
+        <v>3</v>
+      </c>
+      <c r="G7" s="3">
+        <v>3</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K7" s="3">
+        <v>3</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="B8" s="3">
+        <v>3</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="B9" s="3">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="3">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3">
+        <v>5</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K9" s="3">
+        <v>5</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="B10" s="3">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="3">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3">
+        <v>11</v>
+      </c>
+      <c r="F10" s="3">
+        <v>11</v>
+      </c>
+      <c r="G10" s="3">
+        <v>11</v>
+      </c>
+      <c r="H10" s="3">
+        <v>11</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K10" s="3">
+        <v>11</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="B11" s="3">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="B12" s="3">
+        <v>7</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="B13" s="3">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="B14" s="3">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="B15" s="3">
+        <v>10</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="B16" s="3">
+        <v>11</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="目次!A1" display="目次" xr:uid="{9D46B8D9-0325-4BC6-9DAC-DE80F7D28398}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE56C44-4667-470E-9226-94958812C4D7}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="3.5" defaultRowHeight="18.45"/>
